--- a/lib/reports/templates/frekansiyel-rapor-tek.xlsx
+++ b/lib/reports/templates/frekansiyel-rapor-tek.xlsx
@@ -100715,7 +100715,8 @@
       <c r="X25" s="45"/>
       <c r="Y25" s="45"/>
       <c r="Z25" s="47">
-        <v>0.83579999999999999</v>
+        <f>K11</f>
+        <v>0.8358</v>
       </c>
       <c r="AA25" s="47"/>
     </row>
